--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487144_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487144_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4814</v>
+        <v>6.8833</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9106</v>
+        <v>8.0716</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4292</v>
+        <v>-1.1883</v>
       </c>
       <c r="G2" t="n">
         <v>7.245</v>
@@ -610,13 +610,13 @@
         <v>1.158</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4125</v>
+        <v>-0.0106</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1012</v>
+        <v>0.0599</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3114</v>
+        <v>-0.0704</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7101</v>
+        <v>2.8914</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4187</v>
+        <v>1.1388</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7086</v>
+        <v>1.7526</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4799</v>
+        <v>3.1582</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9437</v>
+        <v>1.416</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4637</v>
+        <v>1.7422</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6636</v>
+        <v>2.2836</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6208</v>
+        <v>1.4696</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0428</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1435</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.5644</v>
+        <v>-0.0537</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.9282</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>-0.386</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1045</v>
+        <v>0.1193</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8276</v>
+        <v>-0.1798</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2769</v>
+        <v>0.2991</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0856</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0856</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4106</v>
+        <v>2.489</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7383</v>
+        <v>4.2779</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6723</v>
+        <v>-1.7889</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1582</v>
+        <v>-0.4799</v>
       </c>
       <c r="H4" t="n">
-        <v>1.416</v>
+        <v>-1.9437</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7422</v>
+        <v>1.4637</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2836</v>
+        <v>2.6636</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4696</v>
+        <v>0.6208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.0428</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8745000000000001</v>
+        <v>-3.1435</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0537</v>
+        <v>-2.5644</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9282</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-1.158</v>
       </c>
       <c r="R4" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3616</v>
+        <v>0.8834</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5803</v>
+        <v>0.6868</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2188</v>
+        <v>0.1966</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.0856</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.0856</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5689</v>
+        <v>0.1208</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7609</v>
+        <v>1.4198</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.192</v>
+        <v>-1.2991</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6177</v>
@@ -844,13 +844,13 @@
         <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4568</v>
+        <v>1.0087</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0801</v>
+        <v>0.739</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3767</v>
+        <v>0.2697</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6562</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>A. LOPEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5609</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4881</v>
+        <v>0.8356</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9272</v>
+        <v>-0.7661</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8043</v>
+        <v>-0.8688</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2128</v>
+        <v>-0.3219</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4084</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2511</v>
+        <v>0.3726</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6338</v>
+        <v>0.3726</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3827</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4468</v>
+        <v>-1.2414</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.421</v>
+        <v>-0.6944</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0257</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3161</v>
+        <v>0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2005</v>
+        <v>0.2664</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4602</v>
+        <v>0.1772</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7403</v>
+        <v>0.0892</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1278</v>
+        <v>0.2859</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3281</v>
+        <v>0.2859</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LOPEZ FERNANDEZ</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3846</v>
+        <v>-0.4255</v>
       </c>
       <c r="E7" t="n">
-        <v>0.435</v>
+        <v>-0.0515</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8197</v>
+        <v>-0.374</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8688</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3219</v>
+        <v>-0.1262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.5405</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3726</v>
+        <v>-0.2329</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3726</v>
+        <v>0.4347</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.6676</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2414</v>
+        <v>-0.4338</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6944</v>
+        <v>-0.5609</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.1271</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1877</v>
+        <v>0.0483</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2234</v>
+        <v>0.1814</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0357</v>
+        <v>-0.1332</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8062</v>
+        <v>-1.663</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3519</v>
+        <v>-0.4146</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4543</v>
+        <v>-1.2484</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6667999999999999</v>
+        <v>1.8043</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1262</v>
+        <v>2.2128</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5405</v>
+        <v>-0.4084</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2329</v>
+        <v>2.2511</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4347</v>
+        <v>2.6338</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6676</v>
+        <v>-0.3827</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4338</v>
+        <v>-0.4468</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5609</v>
+        <v>-0.421</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1271</v>
+        <v>-0.0257</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3325</v>
+        <v>0.9766</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.119</v>
+        <v>0.5576</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2135</v>
+        <v>0.419</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.1278</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2993</v>
+        <v>-1.7742</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2627</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5621</v>
+        <v>-1.6959</v>
       </c>
       <c r="G9" t="n">
         <v>0.4925</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3663</v>
+        <v>0.8913</v>
       </c>
       <c r="T9" t="n">
-        <v>1.125</v>
+        <v>0.784</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2412</v>
+        <v>0.1074</v>
       </c>
       <c r="V9" t="n">
         <v>-1.228</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7482</v>
+        <v>-3.8004</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6508</v>
+        <v>0.1096</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0974</v>
+        <v>-3.91</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6588</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9736</v>
+        <v>-0.0258</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8183</v>
+        <v>-0.0578</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1554</v>
+        <v>0.032</v>
       </c>
       <c r="V10" t="n">
         <v>0.0422</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.4936</v>
+        <v>4.790900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>15.0116</v>
+        <v>15.3089</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.5182</v>
+        <v>-10.5181</v>
       </c>
       <c r="G11" t="n">
         <v>7.408000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>9.999999999987796e-05</v>
+        <v>9.999999999965592e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>7.407999999999998</v>
+        <v>7.408000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>19.8547</v>
@@ -1300,7 +1300,7 @@
         <v>-11.554</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8926999999999999</v>
+        <v>-0.8927</v>
       </c>
       <c r="P11" t="n">
         <v>-5.7902</v>
@@ -1312,16 +1312,16 @@
         <v>5.789999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8602</v>
+        <v>4.1576</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6507</v>
+        <v>2.9483</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2093</v>
+        <v>1.2094</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9843000000000004</v>
+        <v>-0.9843000000000008</v>
       </c>
       <c r="W11" t="n">
         <v>4.0868</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9171</v>
+        <v>3.9564</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8231</v>
+        <v>5.0234</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9061</v>
+        <v>-1.067</v>
       </c>
       <c r="G12" t="n">
         <v>4.1527</v>
@@ -1390,13 +1390,13 @@
         <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0575</v>
+        <v>0.0968</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2551</v>
+        <v>-0.0548</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3126</v>
+        <v>0.1517</v>
       </c>
       <c r="V12" t="n">
         <v>0.2859</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4237</v>
+        <v>3.4859</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1409</v>
+        <v>6.6416</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7172</v>
+        <v>-3.1557</v>
       </c>
       <c r="G13" t="n">
         <v>1.744</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3432</v>
+        <v>-1.281</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9677</v>
+        <v>-0.467</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3755</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.8999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2605</v>
+        <v>0.3983</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7825</v>
+        <v>3.0815</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.522</v>
+        <v>-2.6833</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7119</v>
@@ -1546,13 +1546,13 @@
         <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0073</v>
+        <v>0.1451</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7232</v>
+        <v>0.0222</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2842</v>
+        <v>0.1229</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4818</v>
+        <v>-0.4619</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2173</v>
+        <v>-0.1171</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2645</v>
+        <v>-0.3448</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8737</v>
@@ -1624,13 +1624,13 @@
         <v>0.386</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0059</v>
+        <v>0.0258</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2439</v>
+        <v>0.1636</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8012</v>
+        <v>-1.313</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5977</v>
+        <v>-1.6979</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3989</v>
+        <v>0.3849</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3443</v>
+        <v>-1.4458</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5235</v>
+        <v>0.6562</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1792</v>
+        <v>-2.1021</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4837</v>
+        <v>-0.8651</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2162</v>
+        <v>1.0971</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7326</v>
+        <v>-1.9621</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8607</v>
+        <v>-0.5808</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3073</v>
+        <v>-0.4408</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5534</v>
+        <v>-0.14</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>-0.193</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7059</v>
+        <v>0.3259</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0814</v>
+        <v>0.1322</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3755</v>
+        <v>0.1937</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4736</v>
+        <v>-1.4222</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6979</v>
+        <v>-0.1032</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2243</v>
+        <v>-1.3189</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4458</v>
+        <v>-1.3443</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6562</v>
+        <v>-1.5235</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1021</v>
+        <v>0.1792</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8651</v>
+        <v>-0.4837</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0971</v>
+        <v>-1.2162</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9621</v>
+        <v>0.7326</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5808</v>
+        <v>-0.8607</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4408</v>
+        <v>-0.3073</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.14</v>
+        <v>-0.5534</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1653</v>
+        <v>0.0849</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1322</v>
+        <v>0.3804</v>
       </c>
       <c r="U17" t="n">
-        <v>0.033</v>
+        <v>-0.2955</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. DARAME PIZARRO</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7938</v>
+        <v>-1.4679</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1835</v>
+        <v>-1.6391</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6103</v>
+        <v>0.1711</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6708</v>
+        <v>-2.2574</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2752</v>
+        <v>-2.4052</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3956</v>
+        <v>0.1478</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3969</v>
+        <v>-1.069</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3726</v>
+        <v>-0.9626</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0243</v>
+        <v>-0.1064</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0677</v>
+        <v>-1.1884</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6478</v>
+        <v>-1.4426</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4199</v>
+        <v>0.2542</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.158</v>
+        <v>-0.5532</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3847</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5427</v>
+        <v>0.0168</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2014</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2014</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0036</v>
+        <v>-1.8235</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2086</v>
+        <v>0.3088</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2122</v>
+        <v>-2.1322</v>
       </c>
       <c r="G19" t="n">
         <v>-3.1652</v>
@@ -1936,13 +1936,13 @@
         <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7033</v>
+        <v>-0.5232</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>-0.348</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2552</v>
+        <v>-0.1752</v>
       </c>
       <c r="V19" t="n">
         <v>0.8999</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>G. DARAME PIZARRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5572</v>
+        <v>-2.007</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1398</v>
+        <v>-0.584</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4175</v>
+        <v>-1.423</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2574</v>
+        <v>-0.6708</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4052</v>
+        <v>-0.2752</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1478</v>
+        <v>-0.3956</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.069</v>
+        <v>0.3969</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9626</v>
+        <v>0.3726</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1064</v>
+        <v>0.0243</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1884</v>
+        <v>-1.0677</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4426</v>
+        <v>-0.6478</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2542</v>
+        <v>-0.4199</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5441</v>
+        <v>-0.965</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6425</v>
+        <v>-0.3711</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0708</v>
+        <v>-0.0159</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5718</v>
+        <v>-0.3553</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2014</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9836</v>
+        <v>-2.5034</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7965</v>
+        <v>-0.3959</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1872</v>
+        <v>-2.1075</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8355</v>
@@ -2092,13 +2092,13 @@
         <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.4749</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5512</v>
+        <v>-0.1507</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4039</v>
+        <v>-0.3242</v>
       </c>
       <c r="V21" t="n">
         <v>0.614</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.493500000000001</v>
+        <v>-3.158300000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>10.5178</v>
+        <v>10.5181</v>
       </c>
       <c r="F22" t="n">
-        <v>-15.0116</v>
+        <v>-13.6764</v>
       </c>
       <c r="G22" t="n">
         <v>-7.4079</v>
@@ -2170,13 +2170,13 @@
         <v>11.5805</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.8602</v>
+        <v>-2.5249</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2094</v>
+        <v>-1.2095</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.6509</v>
+        <v>-1.3155</v>
       </c>
       <c r="V22" t="n">
         <v>0.9844999999999999</v>
